--- a/AtchisonRegime/Outputs/India/df_regSummary_India.xlsx
+++ b/AtchisonRegime/Outputs/India/df_regSummary_India.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>1.447623304931485</v>
+        <v>1.523484890013984</v>
       </c>
       <c r="H2" t="n">
-        <v>3.236347854694936</v>
+        <v>3.188552233340731</v>
       </c>
       <c r="I2" t="n">
         <v>-4.67741272685366</v>
@@ -545,16 +545,16 @@
         <v>11.6865661939146</v>
       </c>
       <c r="K2" t="n">
-        <v>26.03174603174604</v>
+        <v>27.84810126582278</v>
       </c>
       <c r="L2" t="n">
         <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>11.71428571428571</v>
+        <v>12.57142857142857</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1788072842659378</v>
+        <v>0.2049153621861527</v>
       </c>
       <c r="O2" t="n">
         <v>0.1092691947878082</v>
@@ -603,7 +603,7 @@
         <v>8.087478763970051</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19.9367088607595</v>
       </c>
       <c r="L3" t="n">
         <v>7</v>
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.05996640891228729</v>
+        <v>-0.2307006536680203</v>
       </c>
       <c r="H4" t="n">
-        <v>3.687507216502605</v>
+        <v>3.685484415688703</v>
       </c>
       <c r="I4" t="n">
         <v>-7.89876945774868</v>
@@ -661,22 +661,22 @@
         <v>7.66836368393979</v>
       </c>
       <c r="K4" t="n">
-        <v>27.3015873015873</v>
+        <v>25.63291139240506</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>10.75</v>
+        <v>11.57142857142857</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.007633964608099827</v>
+        <v>-0.02890551693032576</v>
       </c>
       <c r="O4" t="n">
         <v>-0.1830962921115959</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1412669016474817</v>
+        <v>0.1100328124237973</v>
       </c>
     </row>
     <row r="5">
@@ -719,7 +719,7 @@
         <v>9.27806823223732</v>
       </c>
       <c r="K5" t="n">
-        <v>26.66666666666667</v>
+        <v>26.58227848101265</v>
       </c>
       <c r="L5" t="n">
         <v>7</v>
